--- a/ExcelTool/ItemData.xlsx
+++ b/ExcelTool/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17750"/>
+    <workbookView windowHeight="18790"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="538">
   <si>
     <t>idx</t>
   </si>
@@ -149,9 +149,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>str</t>
-  </si>
-  <si>
     <t>白萝卜</t>
   </si>
   <si>
@@ -759,6 +756,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>IconStirFriedWhiteRadishRecipe</t>
     </r>
     <r>
@@ -785,6 +789,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>IconStirFriedWhiteRadishRecipe</t>
     </r>
     <r>
@@ -814,6 +825,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>IconStirFriedWhiteRadishRecipe</t>
     </r>
     <r>
@@ -1274,6 +1292,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>610016+620001+620002+620000</t>
     </r>
     <r>
@@ -1789,10 +1814,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1852,24 +1877,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1882,23 +1892,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1915,7 +1925,46 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1923,37 +1972,6 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1969,25 +1987,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2008,67 +2033,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2080,7 +2051,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2098,13 +2069,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2116,49 +2129,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2176,7 +2177,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2188,7 +2213,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2219,24 +2244,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2259,33 +2271,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -2314,6 +2300,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2322,10 +2347,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2334,133 +2359,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2954,7 +2979,7 @@
         <v>15</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>17</v>
@@ -2971,13 +2996,13 @@
         <v>600000</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="F3" s="4">
         <v>6</v>
@@ -2999,10 +3024,10 @@
         <v>50</v>
       </c>
       <c r="M3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="O3" s="4">
         <v>1</v>
@@ -3016,13 +3041,13 @@
         <v>600001</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="F4" s="4">
         <v>6</v>
@@ -3044,10 +3069,10 @@
         <v>50</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="4">
         <v>1</v>
@@ -3061,13 +3086,13 @@
         <v>600002</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -3089,10 +3114,10 @@
         <v>50</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" s="4">
         <v>1</v>
@@ -3106,13 +3131,13 @@
         <v>600003</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="F6" s="4">
         <v>6</v>
@@ -3134,10 +3159,10 @@
         <v>50</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O6" s="4">
         <v>1</v>
@@ -3151,13 +3176,13 @@
         <v>600004</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="F7" s="4">
         <v>6</v>
@@ -3179,10 +3204,10 @@
         <v>50</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O7" s="4">
         <v>1</v>
@@ -3196,13 +3221,13 @@
         <v>600005</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="F8" s="4">
         <v>6</v>
@@ -3224,10 +3249,10 @@
         <v>50</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O8" s="4">
         <v>1</v>
@@ -3241,13 +3266,13 @@
         <v>600006</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="F9" s="4">
         <v>6</v>
@@ -3269,10 +3294,10 @@
         <v>50</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O9" s="4">
         <v>1</v>
@@ -3286,13 +3311,13 @@
         <v>600007</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F10" s="4">
         <v>6</v>
@@ -3314,10 +3339,10 @@
         <v>50</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O10" s="4">
         <v>1</v>
@@ -3331,13 +3356,13 @@
         <v>600008</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="F11" s="4">
         <v>6</v>
@@ -3359,10 +3384,10 @@
         <v>50</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O11" s="4">
         <v>1</v>
@@ -3376,13 +3401,13 @@
         <v>600009</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="F12" s="4">
         <v>6</v>
@@ -3404,10 +3429,10 @@
         <v>50</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O12" s="4">
         <v>1</v>
@@ -3421,13 +3446,13 @@
         <v>600010</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="F13" s="4">
         <v>6</v>
@@ -3449,10 +3474,10 @@
         <v>50</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O13" s="4">
         <v>1</v>
@@ -3466,13 +3491,13 @@
         <v>600011</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="F14" s="4">
         <v>6</v>
@@ -3494,10 +3519,10 @@
         <v>50</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O14" s="4">
         <v>1</v>
@@ -3511,13 +3536,13 @@
         <v>600012</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="F15" s="4">
         <v>6</v>
@@ -3539,10 +3564,10 @@
         <v>50</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O15" s="4">
         <v>1</v>
@@ -3556,13 +3581,13 @@
         <v>600013</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F16" s="4">
         <v>6</v>
@@ -3584,10 +3609,10 @@
         <v>50</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O16" s="4">
         <v>1</v>
@@ -3601,13 +3626,13 @@
         <v>600014</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="F17" s="4">
         <v>6</v>
@@ -3629,10 +3654,10 @@
         <v>50</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O17" s="4">
         <v>1</v>
@@ -3646,13 +3671,13 @@
         <v>600015</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="F18" s="4">
         <v>6</v>
@@ -3674,10 +3699,10 @@
         <v>50</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O18" s="4">
         <v>1</v>
@@ -3691,13 +3716,13 @@
         <v>600016</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="F19" s="4">
         <v>6</v>
@@ -3719,10 +3744,10 @@
         <v>50</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O19" s="4">
         <v>1</v>
@@ -3736,13 +3761,13 @@
         <v>600017</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="F20" s="4">
         <v>6</v>
@@ -3764,10 +3789,10 @@
         <v>50</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O20" s="4">
         <v>1</v>
@@ -3781,13 +3806,13 @@
         <v>600018</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="F21" s="4">
         <v>6</v>
@@ -3809,10 +3834,10 @@
         <v>50</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O21" s="4">
         <v>1</v>
@@ -3826,13 +3851,13 @@
         <v>600019</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="F22" s="4">
         <v>6</v>
@@ -3854,10 +3879,10 @@
         <v>50</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O22" s="4">
         <v>1</v>
@@ -3871,13 +3896,13 @@
         <v>610000</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="F23" s="4">
         <v>6</v>
@@ -3899,7 +3924,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6">
@@ -3914,13 +3939,13 @@
         <v>610001</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="F24" s="4">
         <v>6</v>
@@ -3942,7 +3967,7 @@
         <v>50</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6">
@@ -3957,13 +3982,13 @@
         <v>610002</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="F25" s="4">
         <v>6</v>
@@ -3985,7 +4010,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6">
@@ -4000,13 +4025,13 @@
         <v>610003</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="F26" s="4">
         <v>6</v>
@@ -4028,7 +4053,7 @@
         <v>50</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6">
@@ -4043,13 +4068,13 @@
         <v>610004</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="F27" s="4">
         <v>6</v>
@@ -4071,7 +4096,7 @@
         <v>50</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6">
@@ -4086,13 +4111,13 @@
         <v>610005</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="F28" s="4">
         <v>6</v>
@@ -4114,7 +4139,7 @@
         <v>50</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N28" s="8"/>
       <c r="O28" s="6">
@@ -4129,13 +4154,13 @@
         <v>610006</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="F29" s="4">
         <v>6</v>
@@ -4157,7 +4182,7 @@
         <v>50</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N29" s="8"/>
       <c r="O29" s="6">
@@ -4172,13 +4197,13 @@
         <v>610007</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="F30" s="4">
         <v>6</v>
@@ -4200,7 +4225,7 @@
         <v>100</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N30" s="8"/>
       <c r="O30" s="8">
@@ -4215,13 +4240,13 @@
         <v>610008</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="F31" s="4">
         <v>6</v>
@@ -4243,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N31" s="8"/>
       <c r="O31" s="8">
@@ -4258,13 +4283,13 @@
         <v>610009</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="F32" s="4">
         <v>6</v>
@@ -4286,7 +4311,7 @@
         <v>100</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N32" s="8"/>
       <c r="O32" s="8">
@@ -4301,13 +4326,13 @@
         <v>610010</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="F33" s="4">
         <v>6</v>
@@ -4329,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N33" s="8"/>
       <c r="O33" s="8">
@@ -4344,13 +4369,13 @@
         <v>610011</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="F34" s="4">
         <v>6</v>
@@ -4372,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N34" s="8"/>
       <c r="O34" s="8">
@@ -4387,13 +4412,13 @@
         <v>610012</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="F35" s="4">
         <v>6</v>
@@ -4415,7 +4440,7 @@
         <v>100</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N35" s="8"/>
       <c r="O35" s="8">
@@ -4430,13 +4455,13 @@
         <v>610013</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="F36" s="4">
         <v>6</v>
@@ -4458,7 +4483,7 @@
         <v>150</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N36" s="8"/>
       <c r="O36" s="8">
@@ -4473,13 +4498,13 @@
         <v>610014</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="F37" s="4">
         <v>6</v>
@@ -4501,7 +4526,7 @@
         <v>150</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N37" s="8"/>
       <c r="O37" s="8">
@@ -4516,13 +4541,13 @@
         <v>610015</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="F38" s="4">
         <v>6</v>
@@ -4544,7 +4569,7 @@
         <v>150</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N38" s="8"/>
       <c r="O38" s="8">
@@ -4559,13 +4584,13 @@
         <v>610016</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="F39" s="4">
         <v>6</v>
@@ -4587,7 +4612,7 @@
         <v>150</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N39" s="8"/>
       <c r="O39" s="8">
@@ -4602,13 +4627,13 @@
         <v>610017</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="F40" s="4">
         <v>6</v>
@@ -4630,7 +4655,7 @@
         <v>150</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N40" s="8"/>
       <c r="O40" s="8">
@@ -4645,13 +4670,13 @@
         <v>610018</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="F41" s="4">
         <v>6</v>
@@ -4673,7 +4698,7 @@
         <v>200</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N41" s="8"/>
       <c r="O41" s="8">
@@ -4688,13 +4713,13 @@
         <v>610019</v>
       </c>
       <c r="C42" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="F42" s="4">
         <v>6</v>
@@ -4716,7 +4741,7 @@
         <v>200</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N42" s="8"/>
       <c r="O42" s="8">
@@ -4731,13 +4756,13 @@
         <v>620000</v>
       </c>
       <c r="C43" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="F43" s="4">
         <v>6</v>
@@ -4759,7 +4784,7 @@
         <v>50</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N43" s="8"/>
       <c r="O43" s="8">
@@ -4774,13 +4799,13 @@
         <v>620001</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="F44" s="4">
         <v>6</v>
@@ -4802,7 +4827,7 @@
         <v>50</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N44" s="8"/>
       <c r="O44" s="8">
@@ -4817,13 +4842,13 @@
         <v>620002</v>
       </c>
       <c r="C45" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="F45" s="4">
         <v>6</v>
@@ -4845,7 +4870,7 @@
         <v>50</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N45" s="8"/>
       <c r="O45" s="8">
@@ -4860,13 +4885,13 @@
         <v>620003</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="F46" s="4">
         <v>6</v>
@@ -4888,7 +4913,7 @@
         <v>100</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N46" s="8"/>
       <c r="O46" s="8">
@@ -4903,13 +4928,13 @@
         <v>620004</v>
       </c>
       <c r="C47" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="F47" s="4">
         <v>6</v>
@@ -4931,7 +4956,7 @@
         <v>100</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N47" s="8"/>
       <c r="O47" s="8">
@@ -4946,13 +4971,13 @@
         <v>620005</v>
       </c>
       <c r="C48" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="F48" s="4">
         <v>6</v>
@@ -4974,7 +4999,7 @@
         <v>100</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N48" s="8"/>
       <c r="O48" s="8">
@@ -4989,13 +5014,13 @@
         <v>620006</v>
       </c>
       <c r="C49" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="F49" s="4">
         <v>6</v>
@@ -5017,7 +5042,7 @@
         <v>150</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N49" s="8"/>
       <c r="O49" s="8">
@@ -5032,13 +5057,13 @@
         <v>620007</v>
       </c>
       <c r="C50" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>210</v>
       </c>
       <c r="F50" s="4">
         <v>6</v>
@@ -5060,7 +5085,7 @@
         <v>150</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N50" s="8"/>
       <c r="O50" s="8">
@@ -5075,13 +5100,13 @@
         <v>620008</v>
       </c>
       <c r="C51" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>214</v>
       </c>
       <c r="F51" s="4">
         <v>6</v>
@@ -5103,7 +5128,7 @@
         <v>200</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8">
@@ -5118,13 +5143,13 @@
         <v>620009</v>
       </c>
       <c r="C52" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="F52" s="4">
         <v>6</v>
@@ -5146,7 +5171,7 @@
         <v>200</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N52" s="8"/>
       <c r="O52" s="8">
@@ -5161,19 +5186,19 @@
         <v>700000</v>
       </c>
       <c r="C53" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="F53" s="7">
         <v>7</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H53" s="8">
         <v>800001</v>
@@ -5191,7 +5216,7 @@
         <v>1000</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N53" s="8"/>
       <c r="O53" s="10">
@@ -5206,19 +5231,19 @@
         <v>700001</v>
       </c>
       <c r="C54" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>227</v>
       </c>
       <c r="F54" s="7">
         <v>7</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H54" s="8">
         <v>800002</v>
@@ -5236,7 +5261,7 @@
         <v>1000</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N54" s="8"/>
       <c r="O54" s="10">
@@ -5251,19 +5276,19 @@
         <v>700002</v>
       </c>
       <c r="C55" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="F55" s="7">
         <v>7</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H55" s="8">
         <v>800003</v>
@@ -5281,7 +5306,7 @@
         <v>1000</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N55" s="8"/>
       <c r="O55" s="10">
@@ -5296,19 +5321,19 @@
         <v>700003</v>
       </c>
       <c r="C56" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>237</v>
       </c>
       <c r="F56" s="7">
         <v>7</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H56" s="8">
         <v>800004</v>
@@ -5326,7 +5351,7 @@
         <v>1000</v>
       </c>
       <c r="M56" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N56" s="8"/>
       <c r="O56" s="10">
@@ -5341,19 +5366,19 @@
         <v>700004</v>
       </c>
       <c r="C57" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="F57" s="7">
         <v>7</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H57" s="8">
         <v>800005</v>
@@ -5371,7 +5396,7 @@
         <v>1000</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N57" s="8"/>
       <c r="O57" s="10">
@@ -5386,19 +5411,19 @@
         <v>700005</v>
       </c>
       <c r="C58" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="F58" s="7">
         <v>7</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H58" s="8">
         <v>800006</v>
@@ -5416,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="M58" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N58" s="8"/>
       <c r="O58" s="10">
@@ -5431,19 +5456,19 @@
         <v>700006</v>
       </c>
       <c r="C59" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="F59" s="7">
         <v>7</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H59" s="8">
         <v>800007</v>
@@ -5461,7 +5486,7 @@
         <v>2000</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N59" s="8"/>
       <c r="O59" s="10">
@@ -5476,19 +5501,19 @@
         <v>700007</v>
       </c>
       <c r="C60" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="E60" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="F60" s="7">
         <v>7</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H60" s="8">
         <v>800008</v>
@@ -5506,7 +5531,7 @@
         <v>1000</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N60" s="8"/>
       <c r="O60" s="10">
@@ -5521,19 +5546,19 @@
         <v>700008</v>
       </c>
       <c r="C61" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="E61" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="F61" s="7">
         <v>7</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H61" s="8">
         <v>800009</v>
@@ -5551,7 +5576,7 @@
         <v>2000</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N61" s="8"/>
       <c r="O61" s="10">
@@ -5566,19 +5591,19 @@
         <v>700009</v>
       </c>
       <c r="C62" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="F62" s="7">
         <v>7</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H62" s="8">
         <v>800010</v>
@@ -5596,7 +5621,7 @@
         <v>2000</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N62" s="8"/>
       <c r="O62" s="10">
@@ -5611,19 +5636,19 @@
         <v>700010</v>
       </c>
       <c r="C63" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="E63" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="F63" s="7">
         <v>7</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H63" s="8">
         <v>800011</v>
@@ -5641,7 +5666,7 @@
         <v>2000</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N63" s="8"/>
       <c r="O63" s="10">
@@ -5656,19 +5681,19 @@
         <v>700011</v>
       </c>
       <c r="C64" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>277</v>
       </c>
       <c r="F64" s="7">
         <v>7</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H64" s="8">
         <v>800012</v>
@@ -5686,7 +5711,7 @@
         <v>2000</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N64" s="8"/>
       <c r="O64" s="10">
@@ -5701,19 +5726,19 @@
         <v>700012</v>
       </c>
       <c r="C65" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="F65" s="7">
         <v>7</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H65" s="8">
         <v>800013</v>
@@ -5731,7 +5756,7 @@
         <v>2000</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N65" s="8"/>
       <c r="O65" s="10">
@@ -5746,19 +5771,19 @@
         <v>700013</v>
       </c>
       <c r="C66" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="F66" s="7">
         <v>7</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H66" s="8">
         <v>800014</v>
@@ -5776,7 +5801,7 @@
         <v>2000</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N66" s="8"/>
       <c r="O66" s="10">
@@ -5791,19 +5816,19 @@
         <v>700014</v>
       </c>
       <c r="C67" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="E67" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="F67" s="7">
         <v>7</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H67" s="8">
         <v>800015</v>
@@ -5821,7 +5846,7 @@
         <v>1000</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N67" s="8"/>
       <c r="O67" s="10">
@@ -5836,19 +5861,19 @@
         <v>700015</v>
       </c>
       <c r="C68" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="E68" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>297</v>
       </c>
       <c r="F68" s="7">
         <v>7</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H68" s="8">
         <v>800016</v>
@@ -5866,7 +5891,7 @@
         <v>2000</v>
       </c>
       <c r="M68" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N68" s="8"/>
       <c r="O68" s="10">
@@ -5881,19 +5906,19 @@
         <v>700016</v>
       </c>
       <c r="C69" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="E69" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="F69" s="7">
         <v>7</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H69" s="8">
         <v>800017</v>
@@ -5911,7 +5936,7 @@
         <v>2000</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N69" s="8"/>
       <c r="O69" s="10">
@@ -5926,19 +5951,19 @@
         <v>700017</v>
       </c>
       <c r="C70" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="E70" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="F70" s="7">
         <v>7</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H70" s="8">
         <v>800018</v>
@@ -5956,7 +5981,7 @@
         <v>2000</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N70" s="8"/>
       <c r="O70" s="10">
@@ -5971,19 +5996,19 @@
         <v>700018</v>
       </c>
       <c r="C71" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="F71" s="7">
         <v>7</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H71" s="8">
         <v>800019</v>
@@ -6001,7 +6026,7 @@
         <v>2000</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N71" s="8"/>
       <c r="O71" s="10">
@@ -6016,19 +6041,19 @@
         <v>700019</v>
       </c>
       <c r="C72" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="F72" s="7">
         <v>7</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H72" s="8">
         <v>800020</v>
@@ -6046,7 +6071,7 @@
         <v>2000</v>
       </c>
       <c r="M72" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N72" s="8"/>
       <c r="O72" s="10">
@@ -6061,19 +6086,19 @@
         <v>700020</v>
       </c>
       <c r="C73" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="E73" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="F73" s="7">
         <v>7</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H73" s="8">
         <v>800021</v>
@@ -6091,7 +6116,7 @@
         <v>2000</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N73" s="8"/>
       <c r="O73" s="10">
@@ -6106,19 +6131,19 @@
         <v>700021</v>
       </c>
       <c r="C74" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="E74" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="F74" s="7">
         <v>7</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H74" s="8">
         <v>800022</v>
@@ -6136,7 +6161,7 @@
         <v>3000</v>
       </c>
       <c r="M74" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N74" s="8"/>
       <c r="O74" s="10">
@@ -6151,19 +6176,19 @@
         <v>700022</v>
       </c>
       <c r="C75" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="F75" s="7">
         <v>7</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H75" s="8">
         <v>800023</v>
@@ -6181,7 +6206,7 @@
         <v>3000</v>
       </c>
       <c r="M75" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N75" s="8"/>
       <c r="O75" s="10">
@@ -6196,19 +6221,19 @@
         <v>700023</v>
       </c>
       <c r="C76" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>337</v>
       </c>
       <c r="F76" s="7">
         <v>7</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H76" s="8">
         <v>800024</v>
@@ -6226,7 +6251,7 @@
         <v>3000</v>
       </c>
       <c r="M76" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N76" s="8"/>
       <c r="O76" s="10">
@@ -6241,19 +6266,19 @@
         <v>700024</v>
       </c>
       <c r="C77" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="E77" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="F77" s="7">
         <v>7</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H77" s="8">
         <v>800025</v>
@@ -6271,7 +6296,7 @@
         <v>3000</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N77" s="8"/>
       <c r="O77" s="10">
@@ -6286,19 +6311,19 @@
         <v>700025</v>
       </c>
       <c r="C78" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="E78" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="F78" s="7">
         <v>7</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H78" s="8">
         <v>800026</v>
@@ -6316,7 +6341,7 @@
         <v>3000</v>
       </c>
       <c r="M78" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N78" s="8"/>
       <c r="O78" s="10">
@@ -6331,19 +6356,19 @@
         <v>700026</v>
       </c>
       <c r="C79" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>352</v>
       </c>
       <c r="F79" s="7">
         <v>7</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H79" s="8">
         <v>800027</v>
@@ -6361,7 +6386,7 @@
         <v>3000</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N79" s="8"/>
       <c r="O79" s="10">
@@ -6376,19 +6401,19 @@
         <v>700027</v>
       </c>
       <c r="C80" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="F80" s="7">
         <v>7</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H80" s="8">
         <v>800028</v>
@@ -6406,7 +6431,7 @@
         <v>4000</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N80" s="8"/>
       <c r="O80" s="10">
@@ -6421,19 +6446,19 @@
         <v>700028</v>
       </c>
       <c r="C81" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>362</v>
       </c>
       <c r="F81" s="7">
         <v>7</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H81" s="8">
         <v>800029</v>
@@ -6451,7 +6476,7 @@
         <v>3000</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N81" s="8"/>
       <c r="O81" s="10">
@@ -6466,19 +6491,19 @@
         <v>700029</v>
       </c>
       <c r="C82" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="F82" s="7">
         <v>7</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H82" s="8">
         <v>800030</v>
@@ -6496,7 +6521,7 @@
         <v>3000</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N82" s="8"/>
       <c r="O82" s="10">
@@ -6511,19 +6536,19 @@
         <v>700030</v>
       </c>
       <c r="C83" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="F83" s="7">
         <v>7</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H83" s="8">
         <v>800031</v>
@@ -6541,7 +6566,7 @@
         <v>4000</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N83" s="8"/>
       <c r="O83" s="10">
@@ -6556,19 +6581,19 @@
         <v>700031</v>
       </c>
       <c r="C84" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="E84" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="F84" s="7">
         <v>7</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H84" s="8">
         <v>800032</v>
@@ -6586,7 +6611,7 @@
         <v>3000</v>
       </c>
       <c r="M84" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N84" s="8"/>
       <c r="O84" s="10">
@@ -6601,19 +6626,19 @@
         <v>700032</v>
       </c>
       <c r="C85" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="E85" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="F85" s="7">
         <v>7</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H85" s="8">
         <v>800033</v>
@@ -6631,7 +6656,7 @@
         <v>4000</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N85" s="8"/>
       <c r="O85" s="10">
@@ -6646,19 +6671,19 @@
         <v>700033</v>
       </c>
       <c r="C86" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="E86" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="F86" s="7">
         <v>7</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H86" s="8">
         <v>800034</v>
@@ -6676,7 +6701,7 @@
         <v>4000</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N86" s="8"/>
       <c r="O86" s="10">
@@ -6691,19 +6716,19 @@
         <v>700034</v>
       </c>
       <c r="C87" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="E87" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="F87" s="7">
         <v>7</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H87" s="8">
         <v>800035</v>
@@ -6721,7 +6746,7 @@
         <v>1000</v>
       </c>
       <c r="M87" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="N87" s="8"/>
       <c r="O87" s="10">
@@ -6736,13 +6761,13 @@
         <v>800000</v>
       </c>
       <c r="C88" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="E88" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="F88" s="7">
         <v>8</v>
@@ -6762,7 +6787,7 @@
         <v>200</v>
       </c>
       <c r="M88" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N88" s="8"/>
       <c r="O88" s="10">
@@ -6777,13 +6802,13 @@
         <v>800001</v>
       </c>
       <c r="C89" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="E89" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>401</v>
       </c>
       <c r="F89" s="7">
         <v>8</v>
@@ -6803,7 +6828,7 @@
         <v>400</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N89" s="8"/>
       <c r="O89" s="10">
@@ -6818,13 +6843,13 @@
         <v>800002</v>
       </c>
       <c r="C90" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>405</v>
       </c>
       <c r="F90" s="7">
         <v>8</v>
@@ -6844,7 +6869,7 @@
         <v>400</v>
       </c>
       <c r="M90" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N90" s="8"/>
       <c r="O90" s="10">
@@ -6859,13 +6884,13 @@
         <v>800003</v>
       </c>
       <c r="C91" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="E91" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="F91" s="7">
         <v>8</v>
@@ -6885,7 +6910,7 @@
         <v>400</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N91" s="8"/>
       <c r="O91" s="10">
@@ -6900,13 +6925,13 @@
         <v>800004</v>
       </c>
       <c r="C92" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="E92" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>413</v>
       </c>
       <c r="F92" s="7">
         <v>8</v>
@@ -6926,7 +6951,7 @@
         <v>400</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N92" s="8"/>
       <c r="O92" s="10">
@@ -6941,13 +6966,13 @@
         <v>800005</v>
       </c>
       <c r="C93" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="E93" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="F93" s="7">
         <v>8</v>
@@ -6967,7 +6992,7 @@
         <v>400</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N93" s="8"/>
       <c r="O93" s="10">
@@ -6982,13 +7007,13 @@
         <v>800006</v>
       </c>
       <c r="C94" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="E94" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>421</v>
       </c>
       <c r="F94" s="7">
         <v>8</v>
@@ -7008,7 +7033,7 @@
         <v>400</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N94" s="8"/>
       <c r="O94" s="10">
@@ -7023,13 +7048,13 @@
         <v>800007</v>
       </c>
       <c r="C95" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="E95" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="F95" s="7">
         <v>8</v>
@@ -7049,7 +7074,7 @@
         <v>600</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N95" s="8"/>
       <c r="O95" s="10">
@@ -7064,13 +7089,13 @@
         <v>800008</v>
       </c>
       <c r="C96" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D96" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="E96" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="F96" s="7">
         <v>8</v>
@@ -7090,7 +7115,7 @@
         <v>400</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N96" s="8"/>
       <c r="O96" s="10">
@@ -7105,13 +7130,13 @@
         <v>800009</v>
       </c>
       <c r="C97" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="E97" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="E97" s="4" t="s">
-        <v>433</v>
       </c>
       <c r="F97" s="7">
         <v>8</v>
@@ -7131,7 +7156,7 @@
         <v>600</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N97" s="8"/>
       <c r="O97" s="10">
@@ -7146,13 +7171,13 @@
         <v>800010</v>
       </c>
       <c r="C98" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="E98" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="F98" s="7">
         <v>8</v>
@@ -7172,7 +7197,7 @@
         <v>600</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N98" s="8"/>
       <c r="O98" s="10">
@@ -7187,13 +7212,13 @@
         <v>800011</v>
       </c>
       <c r="C99" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="E99" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>441</v>
       </c>
       <c r="F99" s="7">
         <v>8</v>
@@ -7213,7 +7238,7 @@
         <v>600</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N99" s="8"/>
       <c r="O99" s="10">
@@ -7228,13 +7253,13 @@
         <v>800012</v>
       </c>
       <c r="C100" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="E100" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>445</v>
       </c>
       <c r="F100" s="7">
         <v>8</v>
@@ -7254,7 +7279,7 @@
         <v>600</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N100" s="8"/>
       <c r="O100" s="10">
@@ -7269,13 +7294,13 @@
         <v>800013</v>
       </c>
       <c r="C101" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="E101" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="F101" s="7">
         <v>8</v>
@@ -7295,7 +7320,7 @@
         <v>600</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N101" s="8"/>
       <c r="O101" s="10">
@@ -7310,13 +7335,13 @@
         <v>800014</v>
       </c>
       <c r="C102" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="E102" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>453</v>
       </c>
       <c r="F102" s="7">
         <v>8</v>
@@ -7336,7 +7361,7 @@
         <v>600</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N102" s="8"/>
       <c r="O102" s="10">
@@ -7351,13 +7376,13 @@
         <v>800015</v>
       </c>
       <c r="C103" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="E103" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="E103" s="4" t="s">
-        <v>457</v>
       </c>
       <c r="F103" s="7">
         <v>8</v>
@@ -7377,7 +7402,7 @@
         <v>400</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N103" s="8"/>
       <c r="O103" s="10">
@@ -7392,13 +7417,13 @@
         <v>800016</v>
       </c>
       <c r="C104" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="E104" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>461</v>
       </c>
       <c r="F104" s="7">
         <v>8</v>
@@ -7418,7 +7443,7 @@
         <v>600</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N104" s="8"/>
       <c r="O104" s="10">
@@ -7433,13 +7458,13 @@
         <v>800017</v>
       </c>
       <c r="C105" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="D105" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="E105" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>465</v>
       </c>
       <c r="F105" s="7">
         <v>8</v>
@@ -7459,7 +7484,7 @@
         <v>600</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N105" s="8"/>
       <c r="O105" s="10">
@@ -7474,13 +7499,13 @@
         <v>800018</v>
       </c>
       <c r="C106" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="E106" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="F106" s="7">
         <v>8</v>
@@ -7500,7 +7525,7 @@
         <v>600</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N106" s="8"/>
       <c r="O106" s="10">
@@ -7515,13 +7540,13 @@
         <v>800019</v>
       </c>
       <c r="C107" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="E107" s="4" t="s">
         <v>472</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>473</v>
       </c>
       <c r="F107" s="7">
         <v>8</v>
@@ -7541,7 +7566,7 @@
         <v>600</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N107" s="8"/>
       <c r="O107" s="10">
@@ -7556,13 +7581,13 @@
         <v>800020</v>
       </c>
       <c r="C108" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="E108" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="F108" s="7">
         <v>8</v>
@@ -7582,7 +7607,7 @@
         <v>600</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N108" s="8"/>
       <c r="O108" s="10">
@@ -7597,13 +7622,13 @@
         <v>800021</v>
       </c>
       <c r="C109" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="E109" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="F109" s="7">
         <v>8</v>
@@ -7623,7 +7648,7 @@
         <v>600</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N109" s="8"/>
       <c r="O109" s="10">
@@ -7638,13 +7663,13 @@
         <v>800022</v>
       </c>
       <c r="C110" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="E110" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>485</v>
       </c>
       <c r="F110" s="7">
         <v>8</v>
@@ -7664,7 +7689,7 @@
         <v>800</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N110" s="8"/>
       <c r="O110" s="10">
@@ -7679,13 +7704,13 @@
         <v>800023</v>
       </c>
       <c r="C111" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="E111" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="F111" s="7">
         <v>8</v>
@@ -7705,7 +7730,7 @@
         <v>800</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N111" s="8"/>
       <c r="O111" s="10">
@@ -7720,13 +7745,13 @@
         <v>800024</v>
       </c>
       <c r="C112" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="E112" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="F112" s="7">
         <v>8</v>
@@ -7746,7 +7771,7 @@
         <v>800</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N112" s="8"/>
       <c r="O112" s="10">
@@ -7761,13 +7786,13 @@
         <v>800025</v>
       </c>
       <c r="C113" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="E113" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="F113" s="7">
         <v>8</v>
@@ -7787,7 +7812,7 @@
         <v>800</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N113" s="8"/>
       <c r="O113" s="10">
@@ -7802,13 +7827,13 @@
         <v>800026</v>
       </c>
       <c r="C114" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="E114" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="F114" s="7">
         <v>8</v>
@@ -7828,7 +7853,7 @@
         <v>800</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="N114" s="8"/>
       <c r="O114" s="10">
@@ -7843,13 +7868,13 @@
         <v>800027</v>
       </c>
       <c r="C115" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="D115" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>505</v>
       </c>
       <c r="F115" s="7">
         <v>8</v>
@@ -7869,7 +7894,7 @@
         <v>800</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N115" s="8"/>
       <c r="O115" s="10">
@@ -7884,13 +7909,13 @@
         <v>800028</v>
       </c>
       <c r="C116" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="D116" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>509</v>
       </c>
       <c r="F116" s="7">
         <v>8</v>
@@ -7910,7 +7935,7 @@
         <v>1000</v>
       </c>
       <c r="M116" s="10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N116" s="8"/>
       <c r="O116" s="10">
@@ -7925,13 +7950,13 @@
         <v>800029</v>
       </c>
       <c r="C117" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="D117" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="E117" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="F117" s="7">
         <v>8</v>
@@ -7951,7 +7976,7 @@
         <v>800</v>
       </c>
       <c r="M117" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="N117" s="8"/>
       <c r="O117" s="10">
@@ -7966,13 +7991,13 @@
         <v>800030</v>
       </c>
       <c r="C118" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="D118" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="E118" s="4" t="s">
         <v>516</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>517</v>
       </c>
       <c r="F118" s="7">
         <v>8</v>
@@ -7992,7 +8017,7 @@
         <v>800</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N118" s="8"/>
       <c r="O118" s="10">
@@ -8007,13 +8032,13 @@
         <v>800031</v>
       </c>
       <c r="C119" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="E119" s="4" t="s">
         <v>520</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>521</v>
       </c>
       <c r="F119" s="7">
         <v>8</v>
@@ -8033,7 +8058,7 @@
         <v>1000</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N119" s="8"/>
       <c r="O119" s="10">
@@ -8048,13 +8073,13 @@
         <v>800032</v>
       </c>
       <c r="C120" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D120" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="E120" s="4" t="s">
         <v>524</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>525</v>
       </c>
       <c r="F120" s="7">
         <v>8</v>
@@ -8074,7 +8099,7 @@
         <v>800</v>
       </c>
       <c r="M120" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N120" s="8"/>
       <c r="O120" s="10">
@@ -8089,13 +8114,13 @@
         <v>800033</v>
       </c>
       <c r="C121" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="E121" s="4" t="s">
         <v>528</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="F121" s="7">
         <v>8</v>
@@ -8115,7 +8140,7 @@
         <v>1000</v>
       </c>
       <c r="M121" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="N121" s="8"/>
       <c r="O121" s="10">
@@ -8130,13 +8155,13 @@
         <v>800034</v>
       </c>
       <c r="C122" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="E122" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="F122" s="7">
         <v>8</v>
@@ -8156,7 +8181,7 @@
         <v>1000</v>
       </c>
       <c r="M122" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N122" s="8"/>
       <c r="O122" s="10">
@@ -8171,13 +8196,13 @@
         <v>800035</v>
       </c>
       <c r="C123" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="F123" s="7">
         <v>8</v>
@@ -8197,7 +8222,7 @@
         <v>400</v>
       </c>
       <c r="M123" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N123" s="8"/>
       <c r="O123" s="10">
